--- a/ExactMass_Impurities_Calc.xlsx
+++ b/ExactMass_Impurities_Calc.xlsx
@@ -2147,7 +2147,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   并对每个杂质用 ExactMass_Calculator_v2 的引擎计算其理论同位素峰（前20峰）</t>
+          <t xml:space="preserve">   并对每个杂质用 ExactMass_Calculator_v2 的引擎计算其理论同位素峰（前50峰）</t>
         </is>
       </c>
     </row>
